--- a/output/graficos_regionales_piramide/plot_comunal_piramide_2020_antofagasta.xlsx
+++ b/output/graficos_regionales_piramide/plot_comunal_piramide_2020_antofagasta.xlsx
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-30 15:41</t>
+    <t xml:space="preserve">2026-10-05 21:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
